--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N65_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N65_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62.88550525113624</v>
+        <v>10.21889460330964</v>
       </c>
       <c r="D2" t="n">
-        <v>21.56220654941034</v>
+        <v>3.50385856427918</v>
       </c>
       <c r="E2" t="n">
-        <v>9.157726441613519</v>
+        <v>1.488130546762196</v>
       </c>
       <c r="F2" t="n">
-        <v>3.393989870645065</v>
+        <v>0.551523353979823</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.57005236790921</v>
+        <v>7.242633509785247</v>
       </c>
       <c r="D3" t="n">
-        <v>14.77422680812021</v>
+        <v>2.400811856319534</v>
       </c>
       <c r="E3" t="n">
-        <v>9.157726441613519</v>
+        <v>1.488130546762196</v>
       </c>
       <c r="F3" t="n">
-        <v>3.393989870645065</v>
+        <v>0.551523353979823</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
